--- a/sheets/조재수대금교본/검수/천년바위 (2).xlsx
+++ b/sheets/조재수대금교본/검수/천년바위 (2).xlsx
@@ -2874,7 +2874,7 @@
       <c r="K4" s="22"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ㄱ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="M4" s="22"/>
@@ -2893,7 +2893,7 @@
       <c r="Q4" s="22"/>
       <c r="R4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="S4" s="22"/>
@@ -2904,27 +2904,15 @@
       <c r="C5" s="22"/>
       <c r="D5" s="21"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F5" s="21"/>
       <c r="G5" s="22"/>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H5" s="21"/>
       <c r="I5" s="22"/>
       <c r="J5" s="21"/>
       <c r="K5" s="22"/>
       <c r="L5" s="21"/>
       <c r="M5" s="22"/>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N5" s="21"/>
       <c r="O5" s="22"/>
       <c r="P5" s="21"/>
       <c r="Q5" s="22"/>
@@ -2943,11 +2931,7 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21"/>
       <c r="K6" s="22"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="L6" s="21"/>
       <c r="M6" s="22"/>
       <c r="N6" s="21"/>
       <c r="O6" s="22"/>
@@ -2970,11 +2954,7 @@
         </is>
       </c>
       <c r="E7" s="22"/>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F7" s="21"/>
       <c r="G7" s="22"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
@@ -3003,15 +2983,11 @@
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-⊏∼</t>
+∼</t>
         </is>
       </c>
       <c r="Q7" s="22"/>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="R7" s="21"/>
       <c r="S7" s="22"/>
     </row>
     <row r="8" ht="82.33" customHeight="true">
@@ -3048,7 +3024,7 @@
       <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㴌c</t>
+㴌</t>
         </is>
       </c>
       <c r="Q8" s="22"/>
@@ -3062,24 +3038,15 @@
     </row>
     <row r="9" ht="82.33" customHeight="true">
       <c r="A9" s="0"/>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B9" s="21"/>
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="E9" s="22"/>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F9" s="21"/>
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
@@ -3097,24 +3064,20 @@
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">c㴌潢
-ﾉ
-–
-‹</t>
+          <t xml:space="preserve">㴌潢
+–</t>
         </is>
       </c>
       <c r="Q9" s="22"/>
@@ -3163,7 +3126,7 @@
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
-南∽</t>
+南</t>
         </is>
       </c>
       <c r="M10" s="22"/>
@@ -3239,8 +3202,8 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
-–ﾉ</t>
+          <t xml:space="preserve">潢
+–</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -3267,7 +3230,7 @@
       <c r="R12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢ʒ</t>
+潢</t>
         </is>
       </c>
       <c r="S12" s="22"/>
@@ -3345,11 +3308,7 @@
         </is>
       </c>
       <c r="E15" s="22"/>
-      <c r="F15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F15" s="21"/>
       <c r="G15" s="22"/>
       <c r="H15" s="21"/>
       <c r="I15" s="22"/>
@@ -3365,23 +3324,11 @@
         </is>
       </c>
       <c r="M15" s="22"/>
-      <c r="N15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N15" s="21"/>
       <c r="O15" s="22"/>
-      <c r="P15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P15" s="21"/>
       <c r="Q15" s="22"/>
-      <c r="R15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R15" s="21"/>
       <c r="S15" s="22"/>
     </row>
     <row r="16" ht="82.33" customHeight="true">

--- a/sheets/조재수대금교본/검수/천년바위 (2).xlsx
+++ b/sheets/조재수대금교본/검수/천년바위 (2).xlsx
@@ -2874,7 +2874,7 @@
       <c r="K4" s="22"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ㄱ</t>
         </is>
       </c>
       <c r="M4" s="22"/>
@@ -2893,7 +2893,7 @@
       <c r="Q4" s="22"/>
       <c r="R4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="S4" s="22"/>
@@ -2904,15 +2904,27 @@
       <c r="C5" s="22"/>
       <c r="D5" s="21"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="21"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G5" s="22"/>
-      <c r="H5" s="21"/>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I5" s="22"/>
       <c r="J5" s="21"/>
       <c r="K5" s="22"/>
       <c r="L5" s="21"/>
       <c r="M5" s="22"/>
-      <c r="N5" s="21"/>
+      <c r="N5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O5" s="22"/>
       <c r="P5" s="21"/>
       <c r="Q5" s="22"/>
@@ -2931,7 +2943,11 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21"/>
       <c r="K6" s="22"/>
-      <c r="L6" s="21"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="M6" s="22"/>
       <c r="N6" s="21"/>
       <c r="O6" s="22"/>
@@ -2954,7 +2970,11 @@
         </is>
       </c>
       <c r="E7" s="22"/>
-      <c r="F7" s="21"/>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G7" s="22"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
@@ -2983,11 +3003,15 @@
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-∼</t>
+⊏∼</t>
         </is>
       </c>
       <c r="Q7" s="22"/>
-      <c r="R7" s="21"/>
+      <c r="R7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="S7" s="22"/>
     </row>
     <row r="8" ht="82.33" customHeight="true">
@@ -3024,7 +3048,7 @@
       <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㴌</t>
+㴌c</t>
         </is>
       </c>
       <c r="Q8" s="22"/>
@@ -3076,7 +3100,8 @@
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌潢
+          <t xml:space="preserve">c㴌潢
+ﾉ
 –</t>
         </is>
       </c>
@@ -3126,7 +3151,7 @@
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
-南</t>
+南∽</t>
         </is>
       </c>
       <c r="M10" s="22"/>
@@ -3202,8 +3227,8 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-–</t>
+          <t xml:space="preserve">潢ʒ
+–ﾉ</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -3230,7 +3255,7 @@
       <c r="R12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢</t>
+潢ʒ</t>
         </is>
       </c>
       <c r="S12" s="22"/>

--- a/sheets/조재수대금교본/검수/천년바위 (2).xlsx
+++ b/sheets/조재수대금교본/검수/천년바위 (2).xlsx
@@ -2769,30 +2769,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="64.52" customHeight="true">
+    <row r="2" ht="83.33" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="82.33" customHeight="true">
+    <row r="3" ht="106.47" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21"/>
       <c r="C3" s="22"/>
@@ -2838,7 +2838,7 @@
       <c r="R3" s="21"/>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="82.33" customHeight="true">
+    <row r="4" ht="106.47" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="S4" s="22"/>
     </row>
-    <row r="5" ht="82.33" customHeight="true">
+    <row r="5" ht="106.47" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="22"/>
@@ -2931,7 +2931,7 @@
       <c r="R5" s="21"/>
       <c r="S5" s="22"/>
     </row>
-    <row r="6" ht="82.33" customHeight="true">
+    <row r="6" ht="106.47" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -2956,7 +2956,7 @@
       <c r="R6" s="21"/>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="82.33" customHeight="true">
+    <row r="7" ht="106.47" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="82.33" customHeight="true">
+    <row r="8" ht="106.47" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="22"/>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="S8" s="22"/>
     </row>
-    <row r="9" ht="82.33" customHeight="true">
+    <row r="9" ht="106.47" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="82.33" customHeight="true">
+    <row r="10" ht="106.47" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="S10" s="22"/>
     </row>
-    <row r="11" ht="82.33" customHeight="true">
+    <row r="11" ht="106.47" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="82.33" customHeight="true">
+    <row r="12" ht="106.47" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="82.33" customHeight="true">
+    <row r="13" ht="106.47" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="S13" s="22"/>
     </row>
-    <row r="14" ht="82.33" customHeight="true">
+    <row r="14" ht="106.47" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
@@ -3319,7 +3319,7 @@
       <c r="R14" s="21"/>
       <c r="S14" s="22"/>
     </row>
-    <row r="15" ht="82.33" customHeight="true">
+    <row r="15" ht="106.47" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       <c r="R15" s="21"/>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" ht="82.33" customHeight="true">
+    <row r="16" ht="106.47" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="22"/>
@@ -3383,6 +3383,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="48"/>
 </worksheet>
 </file>